--- a/qa-test/tactics.xlsx
+++ b/qa-test/tactics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="tactics" sheetId="1" r:id="rId1"/>
@@ -1942,11 +1942,11 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="32.0740740740741" customWidth="1"/>
-    <col min="3" max="3" width="34.6851851851852" customWidth="1"/>
-    <col min="4" max="4" width="22.3148148148148" customWidth="1"/>
-    <col min="5" max="5" width="38.9259259259259" customWidth="1"/>
+    <col min="3" max="3" width="26.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="31.3703703703704" customWidth="1"/>
+    <col min="5" max="5" width="51.3611111111111" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="7.83333333333333" customWidth="1"/>
+    <col min="7" max="7" width="12.0277777777778" customWidth="1"/>
     <col min="8" max="8" width="51.3611111111111" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1976,7 +1976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:8">
+    <row r="2" ht="302.4" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="409.5" spans="1:8">
+    <row r="3" ht="316.8" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="409.5" spans="1:8">
+    <row r="4" ht="273.6" spans="1:8">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="409.5" spans="1:8">
+    <row r="5" ht="316.8" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="409.5" spans="1:8">
+    <row r="6" ht="216" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="409.5" spans="1:8">
+    <row r="7" ht="288" spans="1:8">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" ht="409.5" spans="1:8">
+    <row r="8" ht="273.6" spans="1:8">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" ht="409.5" spans="1:8">
+    <row r="9" ht="216" spans="1:8">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" ht="409.5" spans="1:8">
+    <row r="10" ht="316.8" spans="1:8">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" ht="409.5" spans="1:8">
+    <row r="11" ht="230.4" spans="1:8">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" ht="409.5" spans="1:8">
+    <row r="12" ht="230.4" spans="1:8">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" ht="409.5" spans="1:8">
+    <row r="13" ht="230.4" spans="1:8">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" ht="409.5" spans="1:8">
+    <row r="14" ht="345.6" spans="1:8">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" ht="409.5" spans="1:8">
+    <row r="15" ht="216" spans="1:8">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" ht="409.5" spans="1:8">
+    <row r="16" ht="273.6" spans="1:8">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" ht="409.5" spans="1:8">
+    <row r="17" ht="345.6" spans="1:8">
       <c r="A17" t="s">
         <v>65</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" ht="409.5" spans="1:8">
+    <row r="18" ht="244.8" spans="1:8">
       <c r="A18" t="s">
         <v>65</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" ht="409.5" spans="1:8">
+    <row r="19" ht="288" spans="1:8">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" ht="409.5" spans="1:8">
+    <row r="20" ht="273.6" spans="1:8">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" ht="409.5" spans="1:8">
+    <row r="21" ht="259.2" spans="1:8">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" ht="409.5" spans="1:8">
+    <row r="22" ht="259.2" spans="1:8">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" ht="409.5" spans="1:8">
+    <row r="23" ht="259.2" spans="1:8">
       <c r="A23" t="s">
         <v>84</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" ht="409.5" spans="1:8">
+    <row r="24" ht="216" spans="1:8">
       <c r="A24" t="s">
         <v>84</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" ht="409.5" spans="1:8">
+    <row r="25" ht="216" spans="1:8">
       <c r="A25" t="s">
         <v>84</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" ht="409.5" spans="1:8">
+    <row r="26" ht="244.8" spans="1:8">
       <c r="A26" t="s">
         <v>84</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" ht="409.5" spans="1:8">
+    <row r="27" ht="302.4" spans="1:8">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" ht="409.5" spans="1:8">
+    <row r="28" ht="403.2" spans="1:8">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" ht="409.5" spans="1:8">
+    <row r="29" ht="374.4" spans="1:8">
       <c r="A29" t="s">
         <v>103</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" ht="409.5" spans="1:8">
+    <row r="30" ht="244.8" spans="1:8">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" ht="409.5" spans="1:8">
+    <row r="31" ht="273.6" spans="1:8">
       <c r="A31" t="s">
         <v>103</v>
       </c>
